--- a/templates/casarte_customer_template.xlsx
+++ b/templates/casarte_customer_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,83 +424,41 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>沟通细节</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>跟进细节</t>
+          <t>省市</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>区县</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>录音文本</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>录音链接</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>性别</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>区县</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>客户是否授权联系</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>录音文本</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>录音链接</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>省市</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>13800138000</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>官网咨询</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>客户对洗衣机感兴趣</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>朝阳区</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="输入错误" error="性别只能输入 male 或 female" promptTitle="提示" prompt="请选择 male(男) 或 female(女)" type="list">
-      <formula1>"male,female"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>